--- a/compare_light_and_dark/light_and_dark_metrics.xlsx
+++ b/compare_light_and_dark/light_and_dark_metrics.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="11070" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Section 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -75,11 +77,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -448,21 +451,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Metrik</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Dark</t>
         </is>
@@ -579,10 +582,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.29865574836731</v>
+        <v>11.43383288383484</v>
       </c>
       <c r="C10" t="n">
-        <v>24.09515762329102</v>
+        <v>15.22903347015381</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +595,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4493769835085011</v>
+        <v>0.4647780176910282</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4319918212912418</v>
+        <v>0.4663063804093411</v>
       </c>
     </row>
     <row r="12">
@@ -609,6 +612,19 @@
       </c>
       <c r="C12" t="n">
         <v>7.219268218648373</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cost_function</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9.15949759852959</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.392441938202773</v>
       </c>
     </row>
   </sheetData>
@@ -622,21 +638,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Metrik</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Dark</t>
         </is>
@@ -753,10 +769,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.995909214019768</v>
+        <v>6.796409606933594</v>
       </c>
       <c r="C10" t="n">
-        <v>23.11482000350954</v>
+        <v>6.78495979309082</v>
       </c>
     </row>
     <row r="11">
@@ -766,10 +782,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3254688850691678</v>
+        <v>0.360734472831186</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4121071024039446</v>
+        <v>0.4531914319592923</v>
       </c>
     </row>
     <row r="12">
@@ -783,6 +799,19 @@
       </c>
       <c r="C12" t="n">
         <v>7.104676659622208</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cost_function</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.395692619162472</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.257410216065462</v>
       </c>
     </row>
   </sheetData>
